--- a/registration_forms/050_fitness_coaching_admission_form--registration_forms.xlsx
+++ b/registration_forms/050_fitness_coaching_admission_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
